--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102694</v>
+        <v>102697</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98271</v>
+        <v>98274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102697</v>
+        <v>102698</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98274</v>
+        <v>98275</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531483</v>
       </c>
       <c r="B2" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542890</v>
       </c>
       <c r="B3" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136544487</v>
       </c>
       <c r="B4" t="n">
-        <v>43280</v>
+        <v>43282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102698</v>
+        <v>102703</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98275</v>
+        <v>98280</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102703</v>
+        <v>102705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98280</v>
+        <v>98282</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98282</v>
+        <v>98288</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98288</v>
+        <v>98290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98290</v>
+        <v>98291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98291</v>
+        <v>98297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98297</v>
+        <v>98301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98301</v>
+        <v>98303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98303</v>
+        <v>98305</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531483</v>
       </c>
       <c r="B2" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542890</v>
       </c>
       <c r="B3" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -895,7 +895,7 @@
         <v>136544487</v>
       </c>
       <c r="B4" t="n">
-        <v>43282</v>
+        <v>43295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98305</v>
+        <v>98318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45778-2024 artfynd.xlsx
+++ b/artfynd/A 45778-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136531483</v>
       </c>
       <c r="B2" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542890</v>
       </c>
       <c r="B3" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136544487</v>
       </c>
       <c r="B4" t="n">
-        <v>43295</v>
+        <v>43297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136531547</v>
       </c>
       <c r="B5" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136537491</v>
       </c>
       <c r="B6" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>136540397</v>
       </c>
       <c r="B7" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136545724</v>
       </c>
       <c r="B8" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136545730</v>
       </c>
       <c r="B9" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136533926</v>
       </c>
       <c r="B10" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136534872</v>
       </c>
       <c r="B11" t="n">
-        <v>98318</v>
+        <v>98320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
